--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85A8D35-9EE7-478A-8A62-611FDC0E074D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0446FA82-1266-4612-8B68-B1E85539DFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6060" yWindow="7020" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CurrentInventory" sheetId="1" r:id="rId1"/>
@@ -505,7 +505,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="E2">
         <v>9000</v>
@@ -528,7 +528,7 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E3">
         <v>1600</v>
